--- a/全国各省份PM2.5累计平均_2026年1-3月.xlsx
+++ b/全国各省份PM2.5累计平均_2026年1-3月.xlsx
@@ -945,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -992,7 +992,7 @@
         <v>36.15</v>
       </c>
       <c r="C2" t="n">
-        <v>34.33</v>
+        <v>39.75354838709677</v>
       </c>
       <c r="D2" t="n">
         <v>-0.66</v>
@@ -1000,6 +1000,28 @@
       <c r="E2" t="n">
         <v>-1.8</v>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>西藏</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>浙江</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-1.806451612903226</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1019,6 +1041,25 @@
       <c r="E3" t="n">
         <v>-13.8</v>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>海南</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>18.01</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>西藏</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>-18.3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1038,6 +1079,25 @@
       <c r="E4" t="n">
         <v>-2.2</v>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>28.68</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>-15.6</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1057,6 +1117,25 @@
       <c r="E5" t="n">
         <v>29.1</v>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>内蒙古</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>29.21</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>-13.8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1076,6 +1155,25 @@
       <c r="E6" t="n">
         <v>9.4</v>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>广西</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>-13.8</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1095,6 +1193,25 @@
       <c r="E7" t="n">
         <v>-4.8</v>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>30.03</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>海南</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>-11.8</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1114,6 +1231,25 @@
       <c r="E8" t="n">
         <v>26.4</v>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>31.46</v>
+      </c>
+      <c r="I8" t="n">
+        <v>7</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>-10.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1133,6 +1269,25 @@
       <c r="E9" t="n">
         <v>2.3</v>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>32.15</v>
+      </c>
+      <c r="I9" t="n">
+        <v>8</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>甘肃</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>-10.3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1152,16 +1307,29 @@
       <c r="E10" t="n">
         <v>-5.6</v>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>35.68</v>
+      </c>
+      <c r="I10" t="n">
+        <v>9</v>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>西藏</t>
         </is>
       </c>
-      <c r="K10" t="n">
-        <v>12.45</v>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
       </c>
       <c r="L10" t="n">
-        <v>39.35258064516129</v>
+        <v>-9.9</v>
       </c>
     </row>
     <row r="11">
@@ -1182,16 +1350,29 @@
       <c r="E11" t="n">
         <v>32.3</v>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="I11" t="n">
+        <v>10</v>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>海南</t>
         </is>
       </c>
-      <c r="K11" t="n">
-        <v>15.88</v>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>新疆</t>
+        </is>
       </c>
       <c r="L11" t="n">
-        <v>39.35258064516129</v>
+        <v>-8.699999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1212,16 +1393,29 @@
       <c r="E12" t="n">
         <v>18</v>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>江西</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>11</v>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>福建</t>
         </is>
       </c>
-      <c r="K12" t="n">
-        <v>24.88</v>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
       </c>
       <c r="L12" t="n">
-        <v>39.35258064516129</v>
+        <v>-8.699999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1242,16 +1436,29 @@
       <c r="E13" t="n">
         <v>-8.199999999999999</v>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>浙江</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>38.01</v>
+      </c>
+      <c r="I13" t="n">
+        <v>12</v>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>广东</t>
         </is>
       </c>
-      <c r="K13" t="n">
-        <v>26.33</v>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>黑龙江</t>
+        </is>
       </c>
       <c r="L13" t="n">
-        <v>39.35258064516129</v>
+        <v>-8.4</v>
       </c>
     </row>
     <row r="14">
@@ -1272,16 +1479,29 @@
       <c r="E14" t="n">
         <v>-13.8</v>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="I14" t="n">
+        <v>13</v>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>云南</t>
         </is>
       </c>
-      <c r="K14" t="n">
-        <v>27.11</v>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
       </c>
       <c r="L14" t="n">
-        <v>39.35258064516129</v>
+        <v>-8.199999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1302,16 +1522,29 @@
       <c r="E15" t="n">
         <v>-8.699999999999999</v>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>黑龙江</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>38.92</v>
+      </c>
+      <c r="I15" t="n">
+        <v>14</v>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>内蒙古</t>
         </is>
       </c>
-      <c r="K15" t="n">
-        <v>28.56</v>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
       </c>
       <c r="L15" t="n">
-        <v>39.35258064516129</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="16">
@@ -1332,16 +1565,29 @@
       <c r="E16" t="n">
         <v>-0.1</v>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>广西</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>40.71</v>
+      </c>
+      <c r="I16" t="n">
+        <v>15</v>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>贵州</t>
         </is>
       </c>
-      <c r="K16" t="n">
-        <v>28.76</v>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
       </c>
       <c r="L16" t="n">
-        <v>39.35258064516129</v>
+        <v>-7.2</v>
       </c>
     </row>
     <row r="17">
@@ -1362,16 +1608,29 @@
       <c r="E17" t="n">
         <v>-5.8</v>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>41.74</v>
+      </c>
+      <c r="I17" t="n">
+        <v>16</v>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>浙江</t>
         </is>
       </c>
-      <c r="K17" t="n">
-        <v>30.97</v>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>江西</t>
+        </is>
       </c>
       <c r="L17" t="n">
-        <v>39.35258064516129</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="18">
@@ -1392,16 +1651,29 @@
       <c r="E18" t="n">
         <v>21.4</v>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>吉林</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>41.96</v>
+      </c>
+      <c r="I18" t="n">
+        <v>17</v>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>青海</t>
         </is>
       </c>
-      <c r="K18" t="n">
-        <v>32.14</v>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
       </c>
       <c r="L18" t="n">
-        <v>39.35258064516129</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="19">
@@ -1422,16 +1694,29 @@
       <c r="E19" t="n">
         <v>4</v>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>42</v>
+      </c>
+      <c r="I19" t="n">
+        <v>18</v>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>广西</t>
         </is>
       </c>
-      <c r="K19" t="n">
-        <v>35.07</v>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
       </c>
       <c r="L19" t="n">
-        <v>39.35258064516129</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="20">
@@ -1452,16 +1737,29 @@
       <c r="E20" t="n">
         <v>-18.5</v>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>甘肃</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>19</v>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>重庆</t>
         </is>
       </c>
-      <c r="K20" t="n">
-        <v>35.12</v>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
       </c>
       <c r="L20" t="n">
-        <v>39.35258064516129</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="21">
@@ -1482,16 +1780,29 @@
       <c r="E21" t="n">
         <v>-11.8</v>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>43.26</v>
+      </c>
+      <c r="I21" t="n">
+        <v>20</v>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
-      <c r="K21" t="n">
-        <v>35.49</v>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
       </c>
       <c r="L21" t="n">
-        <v>39.35258064516129</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="22">
@@ -1512,16 +1823,29 @@
       <c r="E22" t="n">
         <v>-2.4</v>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>宁夏</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>43.59</v>
+      </c>
+      <c r="I22" t="n">
+        <v>21</v>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>江西</t>
         </is>
       </c>
-      <c r="K22" t="n">
-        <v>35.61</v>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>内蒙古</t>
+        </is>
       </c>
       <c r="L22" t="n">
-        <v>39.35258064516129</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="23">
@@ -1542,16 +1866,29 @@
       <c r="E23" t="n">
         <v>-5.2</v>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>44.43</v>
+      </c>
+      <c r="I23" t="n">
+        <v>22</v>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="K23" t="n">
-        <v>35.67</v>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
       </c>
       <c r="L23" t="n">
-        <v>39.35258064516129</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="24">
@@ -1572,16 +1909,29 @@
       <c r="E24" t="n">
         <v>-10.3</v>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>45.01</v>
+      </c>
+      <c r="I24" t="n">
+        <v>23</v>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>甘肃</t>
         </is>
       </c>
-      <c r="K24" t="n">
-        <v>38.14</v>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
       </c>
       <c r="L24" t="n">
-        <v>39.35258064516129</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="25">
@@ -1602,16 +1952,29 @@
       <c r="E25" t="n">
         <v>-15.6</v>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>45.62</v>
+      </c>
+      <c r="I25" t="n">
+        <v>24</v>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="K25" t="n">
-        <v>38.78</v>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>宁夏</t>
+        </is>
       </c>
       <c r="L25" t="n">
-        <v>39.35258064516129</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="26">
@@ -1632,16 +1995,29 @@
       <c r="E26" t="n">
         <v>-18.3</v>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>46.26</v>
+      </c>
+      <c r="I26" t="n">
+        <v>25</v>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>四川</t>
         </is>
       </c>
-      <c r="K26" t="n">
-        <v>39.97</v>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
       </c>
       <c r="L26" t="n">
-        <v>39.35258064516129</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1662,16 +2038,29 @@
       <c r="E27" t="n">
         <v>-10.5</v>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>47.11</v>
+      </c>
+      <c r="I27" t="n">
+        <v>26</v>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>辽宁</t>
         </is>
       </c>
-      <c r="K27" t="n">
-        <v>42.33</v>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>吉林</t>
+        </is>
       </c>
       <c r="L27" t="n">
-        <v>39.35258064516129</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="28">
@@ -1692,16 +2081,29 @@
       <c r="E28" t="n">
         <v>-7.2</v>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="I28" t="n">
+        <v>27</v>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>湖南</t>
         </is>
       </c>
-      <c r="K28" t="n">
-        <v>42.67</v>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
       </c>
       <c r="L28" t="n">
-        <v>39.35258064516129</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29">
@@ -1722,16 +2124,29 @@
       <c r="E29" t="n">
         <v>-8.699999999999999</v>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>49.87</v>
+      </c>
+      <c r="I29" t="n">
+        <v>28</v>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>宁夏</t>
         </is>
       </c>
-      <c r="K29" t="n">
-        <v>44.58</v>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
       </c>
       <c r="L29" t="n">
-        <v>39.35258064516129</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="30">
@@ -1752,16 +2167,29 @@
       <c r="E30" t="n">
         <v>-7.3</v>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>51.56</v>
+      </c>
+      <c r="I30" t="n">
+        <v>29</v>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>吉林</t>
         </is>
       </c>
-      <c r="K30" t="n">
-        <v>45.91</v>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
       </c>
       <c r="L30" t="n">
-        <v>39.35258064516129</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="31">
@@ -1782,16 +2210,29 @@
       <c r="E31" t="n">
         <v>-9.9</v>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>52.33</v>
+      </c>
+      <c r="I31" t="n">
+        <v>30</v>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>陕西</t>
         </is>
       </c>
-      <c r="K31" t="n">
-        <v>46.21</v>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
       </c>
       <c r="L31" t="n">
-        <v>39.35258064516129</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="32">
@@ -1812,16 +2253,29 @@
       <c r="E32" t="n">
         <v>-8.4</v>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>新疆</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>67.02</v>
+      </c>
+      <c r="I32" t="n">
+        <v>31</v>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>湖北</t>
         </is>
       </c>
-      <c r="K32" t="n">
-        <v>47</v>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
       </c>
       <c r="L32" t="n">
-        <v>39.35258064516129</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="33">

--- a/全国各省份PM2.5累计平均_2026年1-3月.xlsx
+++ b/全国各省份PM2.5累计平均_2026年1-3月.xlsx
@@ -963,7 +963,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2025年1-3月PM2.5平均值(μg/m³)</t>
+          <t>2026年1-3月份</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>同比变化(μg/m³)</t>
+          <t>2025年1-3月份</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -989,16 +989,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36.15</v>
+        <v>35</v>
       </c>
       <c r="C2" t="n">
-        <v>39.75354838709677</v>
+        <v>40.77</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.66</v>
+        <v>36</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.8</v>
+        <v>-1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1006,21 +1006,21 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>15.23</v>
+        <v>12</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-18.5</v>
+        <v>-9</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.806451612903226</v>
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="3">
@@ -1030,16 +1030,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.46</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n">
         <v>27.63</v>
       </c>
       <c r="D3" t="n">
-        <v>-4.35</v>
+        <v>30</v>
       </c>
       <c r="E3" t="n">
-        <v>-13.8</v>
+        <v>-4</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1047,18 +1047,21 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>18.01</v>
+        <v>19</v>
       </c>
       <c r="I3" t="n">
         <v>2</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-18.3</v>
+        <v>-7</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="4">
@@ -1068,35 +1071,38 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.21</v>
+        <v>29</v>
       </c>
       <c r="C4" t="n">
         <v>27.67</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.65</v>
+        <v>29</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.2</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>28.68</v>
+        <v>26</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-15.6</v>
+        <v>-7</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="5">
@@ -1106,35 +1112,38 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.03</v>
+        <v>39</v>
       </c>
       <c r="C5" t="n">
         <v>38.11</v>
       </c>
       <c r="D5" t="n">
-        <v>8.74</v>
+        <v>30</v>
       </c>
       <c r="E5" t="n">
-        <v>29.1</v>
+        <v>9</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>29.21</v>
+        <v>27</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-13.8</v>
+        <v>-6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="6">
@@ -1144,35 +1153,38 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41.96</v>
+        <v>46</v>
       </c>
       <c r="C6" t="n">
         <v>44.24</v>
       </c>
       <c r="D6" t="n">
-        <v>3.95</v>
+        <v>42</v>
       </c>
       <c r="E6" t="n">
-        <v>9.4</v>
+        <v>4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>29.46</v>
+        <v>29</v>
       </c>
       <c r="I6" t="n">
         <v>5</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-13.8</v>
+        <v>-6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="7">
@@ -1182,35 +1194,38 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C7" t="n">
         <v>36.97</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.03</v>
+        <v>42</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.8</v>
+        <v>-2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>30.03</v>
+        <v>29</v>
       </c>
       <c r="I7" t="n">
         <v>6</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-11.8</v>
+        <v>-4</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="8">
@@ -1220,16 +1235,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>44.43</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
         <v>53.44</v>
       </c>
       <c r="D8" t="n">
-        <v>11.71</v>
+        <v>44</v>
       </c>
       <c r="E8" t="n">
-        <v>26.4</v>
+        <v>12</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1237,18 +1252,21 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>31.46</v>
+        <v>30</v>
       </c>
       <c r="I8" t="n">
         <v>7</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-10.5</v>
+        <v>-4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="9">
@@ -1258,35 +1276,38 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43.59</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
         <v>42.32</v>
       </c>
       <c r="D9" t="n">
-        <v>0.99</v>
+        <v>44</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>32.15</v>
+        <v>30</v>
       </c>
       <c r="I9" t="n">
         <v>8</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-10.3</v>
+        <v>-4</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="10">
@@ -1296,24 +1317,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52.33</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
         <v>46.13</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.92</v>
+        <v>52</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.6</v>
+        <v>-2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>35.68</v>
+        <v>32</v>
       </c>
       <c r="I10" t="n">
         <v>9</v>
@@ -1325,11 +1346,14 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-9.9</v>
+        <v>-4</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="11">
@@ -1339,16 +1363,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>46.26</v>
+        <v>61</v>
       </c>
       <c r="C11" t="n">
         <v>56.52</v>
       </c>
       <c r="D11" t="n">
-        <v>14.92</v>
+        <v>46</v>
       </c>
       <c r="E11" t="n">
-        <v>32.3</v>
+        <v>15</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1356,7 +1380,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>36.15</v>
+        <v>36</v>
       </c>
       <c r="I11" t="n">
         <v>10</v>
@@ -1368,11 +1392,14 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-8.699999999999999</v>
+        <v>-4</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="12">
@@ -1382,24 +1409,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>43.26</v>
+        <v>51</v>
       </c>
       <c r="C12" t="n">
         <v>47.72</v>
       </c>
       <c r="D12" t="n">
-        <v>7.78</v>
+        <v>43</v>
       </c>
       <c r="E12" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>37.8</v>
+        <v>37</v>
       </c>
       <c r="I12" t="n">
         <v>11</v>
@@ -1411,11 +1438,14 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-8.699999999999999</v>
+        <v>-3</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="13">
@@ -1425,24 +1455,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28.68</v>
+        <v>26</v>
       </c>
       <c r="C13" t="n">
         <v>25.29</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.35</v>
+        <v>29</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.199999999999999</v>
+        <v>-3</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>38.01</v>
+        <v>38</v>
       </c>
       <c r="I13" t="n">
         <v>12</v>
@@ -1454,11 +1484,14 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-8.4</v>
+        <v>-3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="14">
@@ -1468,24 +1501,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>40.71</v>
+        <v>35</v>
       </c>
       <c r="C14" t="n">
         <v>35.32</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.64</v>
+        <v>41</v>
       </c>
       <c r="E14" t="n">
-        <v>-13.8</v>
+        <v>-6</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>38.45</v>
+        <v>38</v>
       </c>
       <c r="I14" t="n">
         <v>13</v>
@@ -1497,11 +1530,14 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-8.199999999999999</v>
+        <v>-2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="15">
@@ -1511,24 +1547,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>67.02</v>
+        <v>59</v>
       </c>
       <c r="C15" t="n">
         <v>56.44</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.81</v>
+        <v>63</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.699999999999999</v>
+        <v>-4</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>38.92</v>
+        <v>41</v>
       </c>
       <c r="I15" t="n">
         <v>14</v>
@@ -1540,11 +1576,14 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-7.3</v>
+        <v>-2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="16">
@@ -1554,24 +1593,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>47.11</v>
+        <v>47</v>
       </c>
       <c r="C16" t="n">
         <v>44.82</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.07000000000000001</v>
+        <v>47</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>40.71</v>
+        <v>41</v>
       </c>
       <c r="I16" t="n">
         <v>15</v>
@@ -1583,11 +1622,14 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-7.2</v>
+        <v>-2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="17">
@@ -1597,24 +1639,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>37.8</v>
+        <v>35</v>
       </c>
       <c r="C17" t="n">
         <v>33.59</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.2</v>
+        <v>38</v>
       </c>
       <c r="E17" t="n">
-        <v>-5.8</v>
+        <v>-3</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>41.74</v>
+        <v>42</v>
       </c>
       <c r="I17" t="n">
         <v>16</v>
@@ -1626,11 +1668,14 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-5.8</v>
+        <v>-1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="18">
@@ -1640,24 +1685,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>41.74</v>
+        <v>59</v>
       </c>
       <c r="C18" t="n">
         <v>52.67</v>
       </c>
       <c r="D18" t="n">
-        <v>8.92</v>
+        <v>42</v>
       </c>
       <c r="E18" t="n">
-        <v>21.4</v>
+        <v>17</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>41.96</v>
+        <v>42</v>
       </c>
       <c r="I18" t="n">
         <v>17</v>
@@ -1669,11 +1714,14 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-5.6</v>
+        <v>-1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="19">
@@ -1683,20 +1731,20 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>51.56</v>
+        <v>67</v>
       </c>
       <c r="C19" t="n">
         <v>61.47</v>
       </c>
       <c r="D19" t="n">
-        <v>2.05</v>
+        <v>59</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1712,11 +1760,14 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-5.2</v>
+        <v>-1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="20">
@@ -1726,24 +1777,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>38.01</v>
+        <v>33</v>
       </c>
       <c r="C20" t="n">
         <v>31.62</v>
       </c>
       <c r="D20" t="n">
-        <v>-7.04</v>
+        <v>37</v>
       </c>
       <c r="E20" t="n">
-        <v>-18.5</v>
+        <v>-4</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>42.5</v>
+        <v>43</v>
       </c>
       <c r="I20" t="n">
         <v>19</v>
@@ -1755,11 +1806,14 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-4.8</v>
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="21">
@@ -1769,24 +1823,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18.01</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
         <v>19.23</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.13</v>
+        <v>19</v>
       </c>
       <c r="E21" t="n">
-        <v>-11.8</v>
+        <v>-1</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>43.26</v>
+        <v>44</v>
       </c>
       <c r="I21" t="n">
         <v>20</v>
@@ -1798,11 +1852,14 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-2.4</v>
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="22">
@@ -1812,16 +1869,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>48.15</v>
+        <v>51</v>
       </c>
       <c r="C22" t="n">
         <v>47.63</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.15</v>
+        <v>58</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4</v>
+        <v>-7</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1829,7 +1886,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>43.59</v>
+        <v>44</v>
       </c>
       <c r="I22" t="n">
         <v>21</v>
@@ -1841,11 +1898,14 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-2.2</v>
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="23">
@@ -1855,24 +1915,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>45.01</v>
+        <v>44</v>
       </c>
       <c r="C23" t="n">
         <v>40.82</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.34</v>
+        <v>53</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.2</v>
+        <v>-9</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>44.43</v>
+        <v>46</v>
       </c>
       <c r="I23" t="n">
         <v>22</v>
@@ -1884,11 +1944,14 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-1.8</v>
+        <v>2</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="24">
@@ -1898,24 +1961,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>42.5</v>
+        <v>46</v>
       </c>
       <c r="C24" t="n">
         <v>42.32</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.36</v>
+        <v>38</v>
       </c>
       <c r="E24" t="n">
-        <v>-10.3</v>
+        <v>8</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>45.01</v>
+        <v>47</v>
       </c>
       <c r="I24" t="n">
         <v>23</v>
@@ -1927,11 +1990,14 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-0.1</v>
+        <v>3</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="25">
@@ -1941,16 +2007,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>29.46</v>
+        <v>23</v>
       </c>
       <c r="C25" t="n">
         <v>22.72</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.58</v>
+        <v>27</v>
       </c>
       <c r="E25" t="n">
-        <v>-15.6</v>
+        <v>-4</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1958,7 +2024,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>45.62</v>
+        <v>47</v>
       </c>
       <c r="I25" t="n">
         <v>24</v>
@@ -1970,11 +2036,14 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>4</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="26">
@@ -1984,24 +2053,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>15.23</v>
+        <v>11</v>
       </c>
       <c r="C26" t="n">
         <v>10.35</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.78</v>
+        <v>12</v>
       </c>
       <c r="E26" t="n">
-        <v>-18.3</v>
+        <v>-1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>46.26</v>
+        <v>48</v>
       </c>
       <c r="I26" t="n">
         <v>25</v>
@@ -2013,11 +2082,14 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="27">
@@ -2027,24 +2099,24 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>32.15</v>
+        <v>30</v>
       </c>
       <c r="C27" t="n">
         <v>28.65</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.39</v>
+        <v>32</v>
       </c>
       <c r="E27" t="n">
-        <v>-10.5</v>
+        <v>-2</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>47.11</v>
+        <v>52</v>
       </c>
       <c r="I27" t="n">
         <v>26</v>
@@ -2056,11 +2128,14 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>9.4</v>
+        <v>8</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="28">
@@ -2070,24 +2145,24 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>45.62</v>
+        <v>50</v>
       </c>
       <c r="C28" t="n">
         <v>47.83</v>
       </c>
       <c r="D28" t="n">
-        <v>-3.29</v>
+        <v>47</v>
       </c>
       <c r="E28" t="n">
-        <v>-7.2</v>
+        <v>3</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>48.15</v>
+        <v>52</v>
       </c>
       <c r="I28" t="n">
         <v>27</v>
@@ -2099,11 +2174,14 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>18</v>
+        <v>8</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="29">
@@ -2113,24 +2191,24 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>38.45</v>
+        <v>42</v>
       </c>
       <c r="C29" t="n">
         <v>39.37</v>
       </c>
       <c r="D29" t="n">
-        <v>-3.33</v>
+        <v>48</v>
       </c>
       <c r="E29" t="n">
-        <v>-8.699999999999999</v>
+        <v>-6</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>49.87</v>
+        <v>53</v>
       </c>
       <c r="I29" t="n">
         <v>28</v>
@@ -2142,11 +2220,14 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>21.4</v>
+        <v>9</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="30">
@@ -2156,24 +2237,24 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>49.87</v>
+        <v>48</v>
       </c>
       <c r="C30" t="n">
         <v>45.3</v>
       </c>
       <c r="D30" t="n">
-        <v>-3.66</v>
+        <v>52</v>
       </c>
       <c r="E30" t="n">
-        <v>-7.3</v>
+        <v>-4</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>51.56</v>
+        <v>58</v>
       </c>
       <c r="I30" t="n">
         <v>29</v>
@@ -2189,7 +2270,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>26.4</v>
+        <v>12</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="31">
@@ -2199,24 +2283,24 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>35.68</v>
+        <v>28</v>
       </c>
       <c r="C31" t="n">
         <v>26.08</v>
       </c>
       <c r="D31" t="n">
-        <v>-3.54</v>
+        <v>26</v>
       </c>
       <c r="E31" t="n">
-        <v>-9.9</v>
+        <v>2</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>52.33</v>
+        <v>59</v>
       </c>
       <c r="I31" t="n">
         <v>30</v>
@@ -2228,11 +2312,14 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>29.1</v>
+        <v>15</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="32">
@@ -2242,16 +2329,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>38.92</v>
+        <v>34</v>
       </c>
       <c r="C32" t="n">
         <v>33.7</v>
       </c>
       <c r="D32" t="n">
-        <v>-3.25</v>
+        <v>41</v>
       </c>
       <c r="E32" t="n">
-        <v>-8.4</v>
+        <v>-7</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2259,7 +2346,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>67.02</v>
+        <v>63</v>
       </c>
       <c r="I32" t="n">
         <v>31</v>
@@ -2271,11 +2358,14 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>32.3</v>
+        <v>17</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="33">
